--- a/Digits/Programs On Digits in Number.xlsx
+++ b/Digits/Programs On Digits in Number.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\C, C++ 14\Digits\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="165" windowWidth="7950" windowHeight="8955" tabRatio="742" firstSheet="6" activeTab="8"/>
+    <workbookView xWindow="240" yWindow="165" windowWidth="7950" windowHeight="8955" tabRatio="742" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Digit Sum" sheetId="1" r:id="rId1"/>
@@ -22,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="26">
   <si>
     <t>No</t>
   </si>
@@ -33,18 +38,6 @@
     <t>dSum</t>
   </si>
   <si>
-    <t>0+3</t>
-  </si>
-  <si>
-    <t>3+5</t>
-  </si>
-  <si>
-    <t>8+9</t>
-  </si>
-  <si>
-    <t>17+4</t>
-  </si>
-  <si>
     <t>Temp</t>
   </si>
   <si>
@@ -75,12 +68,6 @@
     <t>ZCnt</t>
   </si>
   <si>
-    <t>Temp % 10</t>
-  </si>
-  <si>
-    <t>dSum+(Temp % 10)</t>
-  </si>
-  <si>
     <t>Cnt</t>
   </si>
   <si>
@@ -103,12 +90,27 @@
   </si>
   <si>
     <t>Cnt_Of_7</t>
+  </si>
+  <si>
+    <t>0 + 3</t>
+  </si>
+  <si>
+    <t>3 + 5</t>
+  </si>
+  <si>
+    <t>8 + 9</t>
+  </si>
+  <si>
+    <t>17 + 4</t>
+  </si>
+  <si>
+    <t>dSum+(Temp%10)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -317,6 +319,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -364,7 +369,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -399,7 +404,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -608,127 +613,101 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B6:F24"/>
+  <dimension ref="B6:E16"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="25.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="2:6" ht="18.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="2:6" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" ht="18.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="2:5" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <v>0</v>
       </c>
       <c r="C8" s="6">
         <v>0</v>
       </c>
-      <c r="D8" s="7">
-        <v>0</v>
-      </c>
-      <c r="E8" s="7"/>
-      <c r="F8" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D8" s="7"/>
+      <c r="E8" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <v>4953</v>
       </c>
       <c r="C9" s="6">
         <v>4953</v>
       </c>
-      <c r="D9" s="7">
-        <v>3</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D9" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C10" s="6">
         <v>495</v>
       </c>
-      <c r="D10" s="7">
-        <v>5</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="8">
+      <c r="D10" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="8">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C11" s="6">
         <v>49</v>
       </c>
-      <c r="D11" s="7">
-        <v>9</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" s="8">
+      <c r="D11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="8">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C12" s="6">
         <v>4</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="13">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="9">
+        <v>0</v>
+      </c>
+      <c r="D13" s="10"/>
+      <c r="E13" s="11"/>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B16" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E12" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" s="8">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="9">
-        <v>0</v>
-      </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="11"/>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B16" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D17" s="12"/>
-    </row>
-    <row r="24" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D24" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -753,11 +732,11 @@
         <v>0</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
@@ -856,16 +835,16 @@
         <v>0</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>1</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
@@ -894,7 +873,7 @@
         <v>3</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F9" s="8">
         <v>3</v>
@@ -908,7 +887,7 @@
         <v>2</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F10" s="8">
         <v>32</v>
@@ -922,7 +901,7 @@
         <v>4</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F11" s="8">
         <v>324</v>
@@ -936,7 +915,7 @@
         <v>6</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F12" s="8">
         <v>3246</v>
@@ -950,7 +929,7 @@
         <v>8</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F13" s="11">
         <v>32468</v>
@@ -970,14 +949,14 @@
         <v>0</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="4" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.25">
@@ -1002,7 +981,7 @@
       </c>
       <c r="D21" s="7"/>
       <c r="E21" s="7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F21" s="8">
         <v>3</v>
@@ -1014,7 +993,7 @@
       </c>
       <c r="D22" s="7"/>
       <c r="E22" s="7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F22" s="8">
         <v>32</v>
@@ -1026,7 +1005,7 @@
       </c>
       <c r="D23" s="7"/>
       <c r="E23" s="7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F23" s="8">
         <v>324</v>
@@ -1038,7 +1017,7 @@
       </c>
       <c r="D24" s="7"/>
       <c r="E24" s="7" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F24" s="8">
         <v>3246</v>
@@ -1050,7 +1029,7 @@
       </c>
       <c r="D25" s="10"/>
       <c r="E25" s="10" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F25" s="11">
         <v>32468</v>
@@ -1084,11 +1063,11 @@
         <v>0</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
@@ -1202,11 +1181,11 @@
         <v>0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G6"/>
     </row>
@@ -1333,11 +1312,11 @@
         <v>0</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="5" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="4:7" ht="18" x14ac:dyDescent="0.25">
@@ -1444,7 +1423,7 @@
   <sheetData>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="2:5" ht="18.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -1453,11 +1432,11 @@
         <v>0</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
@@ -1545,7 +1524,7 @@
   <sheetData>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="2:5" ht="18.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -1554,13 +1533,13 @@
         <v>0</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
@@ -1681,7 +1660,7 @@
   <sheetData>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="2:5" ht="18.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -1690,13 +1669,13 @@
         <v>0</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
